--- a/demo_data/IO_LIST.xlsx
+++ b/demo_data/IO_LIST.xlsx
@@ -630,7 +630,6 @@
           <t>ELECTRICAL ROOM / B5</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>1</v>
       </c>
@@ -661,7 +660,6 @@
         </is>
       </c>
       <c r="V4" s="5" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -682,7 +680,6 @@
           <t>ELECTRICAL ROOM / A5</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
         <v>0</v>
       </c>
@@ -713,7 +710,6 @@
         </is>
       </c>
       <c r="V5" s="5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -767,7 +763,6 @@
         </is>
       </c>
       <c r="V6" s="5" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -788,7 +783,6 @@
           <t>ELECTRICAL ROOM / A5</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
         <v>0</v>
       </c>
@@ -819,7 +813,6 @@
         </is>
       </c>
       <c r="V7" s="5" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -873,7 +866,6 @@
         </is>
       </c>
       <c r="V8" s="5" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -927,7 +919,6 @@
         </is>
       </c>
       <c r="V9" s="5" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -948,7 +939,6 @@
           <t>ELECTRICAL ROOM / B5</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
         <v>1</v>
       </c>
@@ -979,7 +969,6 @@
         </is>
       </c>
       <c r="V10" s="5" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1033,7 +1022,6 @@
         </is>
       </c>
       <c r="V11" s="5" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1054,7 +1042,6 @@
           <t>ELECTRICAL ROOM / A5</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
         <v>0</v>
       </c>
@@ -1085,7 +1072,6 @@
         </is>
       </c>
       <c r="V12" s="5" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1139,7 +1125,6 @@
         </is>
       </c>
       <c r="V13" s="5" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1193,7 +1178,6 @@
         </is>
       </c>
       <c r="V14" s="5" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1214,7 +1198,6 @@
           <t>ELECTRICAL ROOM / B5</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>1</v>
       </c>
@@ -1245,7 +1228,6 @@
         </is>
       </c>
       <c r="V15" s="5" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1299,7 +1281,6 @@
         </is>
       </c>
       <c r="V16" s="5" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1320,7 +1301,6 @@
           <t>ELECTRICAL ROOM / B5</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>1</v>
       </c>
@@ -1351,7 +1331,6 @@
         </is>
       </c>
       <c r="V17" s="5" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1405,7 +1384,6 @@
         </is>
       </c>
       <c r="V18" s="5" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1426,7 +1404,6 @@
           <t>ELECTRICAL ROOM / A5</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
         <v>0</v>
       </c>
@@ -1457,7 +1434,6 @@
         </is>
       </c>
       <c r="V19" s="5" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1478,7 +1454,6 @@
           <t>ELECTRICAL ROOM / B5</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
         <v>1</v>
       </c>
@@ -1509,7 +1484,6 @@
         </is>
       </c>
       <c r="V20" s="5" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1530,7 +1504,6 @@
           <t>ELECTRICAL ROOM / B5</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
         <v>1</v>
       </c>
@@ -1561,7 +1534,6 @@
         </is>
       </c>
       <c r="V21" s="5" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1582,7 +1554,6 @@
           <t>ELECTRICAL ROOM / B5</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
         <v>1</v>
       </c>
@@ -1613,7 +1584,6 @@
         </is>
       </c>
       <c r="V22" s="5" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1634,7 +1604,6 @@
           <t>ELECTRICAL ROOM / B5</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
         <v>1</v>
       </c>
@@ -1665,7 +1634,6 @@
         </is>
       </c>
       <c r="V23" s="5" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1719,7 +1687,6 @@
         </is>
       </c>
       <c r="V24" s="5" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1740,7 +1707,6 @@
           <t>ELECTRICAL ROOM / C5</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
         <v>2</v>
       </c>
@@ -1771,7 +1737,6 @@
         </is>
       </c>
       <c r="V25" s="5" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1825,7 +1790,6 @@
         </is>
       </c>
       <c r="V26" s="5" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1879,7 +1843,6 @@
         </is>
       </c>
       <c r="V27" s="5" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1933,7 +1896,6 @@
         </is>
       </c>
       <c r="V28" s="5" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1987,7 +1949,6 @@
         </is>
       </c>
       <c r="V29" s="5" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2008,7 +1969,6 @@
           <t>ELECTRICAL ROOM / A5</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
         <v>0</v>
       </c>
@@ -2039,7 +1999,6 @@
         </is>
       </c>
       <c r="V30" s="5" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2093,7 +2052,6 @@
         </is>
       </c>
       <c r="V31" s="5" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2147,7 +2105,6 @@
         </is>
       </c>
       <c r="V32" s="5" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2168,7 +2125,6 @@
           <t>ELECTRICAL ROOM / B5</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
         <v>1</v>
       </c>
@@ -2176,7 +2132,7 @@
         <v>5</v>
       </c>
       <c r="H33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2199,7 +2155,6 @@
         </is>
       </c>
       <c r="V33" s="5" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2220,7 +2175,6 @@
           <t>ELECTRICAL ROOM / B5</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
         <v>1</v>
       </c>
@@ -2251,7 +2205,6 @@
         </is>
       </c>
       <c r="V34" s="5" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2305,7 +2258,6 @@
         </is>
       </c>
       <c r="V35" s="5" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2359,7 +2311,6 @@
         </is>
       </c>
       <c r="V36" s="5" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2380,7 +2331,6 @@
           <t>ELECTRICAL ROOM / B5</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
         <v>1</v>
       </c>
@@ -2411,7 +2361,6 @@
         </is>
       </c>
       <c r="V37" s="5" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2432,7 +2381,6 @@
           <t>ELECTRICAL ROOM / A5</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="n">
         <v>0</v>
       </c>
@@ -2440,7 +2388,7 @@
         <v>5</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2463,7 +2411,6 @@
         </is>
       </c>
       <c r="V38" s="5" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2484,7 +2431,6 @@
           <t>ELECTRICAL ROOM / B5</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="n">
         <v>1</v>
       </c>
@@ -2515,7 +2461,6 @@
         </is>
       </c>
       <c r="V39" s="5" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2536,7 +2481,6 @@
           <t>ELECTRICAL ROOM / A5</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="n">
         <v>0</v>
       </c>
@@ -2567,7 +2511,6 @@
         </is>
       </c>
       <c r="V40" s="5" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2588,7 +2531,6 @@
           <t>ELECTRICAL ROOM / B5</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
         <v>1</v>
       </c>
@@ -2619,7 +2561,6 @@
         </is>
       </c>
       <c r="V41" s="5" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2650,7 +2591,7 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2673,7 +2614,6 @@
         </is>
       </c>
       <c r="V42" s="5" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2694,7 +2634,6 @@
           <t>ELECTRICAL ROOM / A5</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
         <v>0</v>
       </c>
@@ -2725,7 +2664,6 @@
         </is>
       </c>
       <c r="V43" s="5" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2746,7 +2684,6 @@
           <t>ELECTRICAL ROOM / B5</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="n">
         <v>1</v>
       </c>
@@ -2777,7 +2714,6 @@
         </is>
       </c>
       <c r="V44" s="5" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2798,7 +2734,6 @@
           <t>ELECTRICAL ROOM / A5</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="n">
         <v>0</v>
       </c>
@@ -2829,7 +2764,6 @@
         </is>
       </c>
       <c r="V45" s="5" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2850,7 +2784,6 @@
           <t>ELECTRICAL ROOM / A5</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
         <v>0</v>
       </c>
@@ -2881,7 +2814,6 @@
         </is>
       </c>
       <c r="V46" s="5" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2902,7 +2834,6 @@
           <t>ELECTRICAL ROOM / C5</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
         <v>2</v>
       </c>
@@ -2933,7 +2864,6 @@
         </is>
       </c>
       <c r="V47" s="5" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2954,7 +2884,6 @@
           <t>ELECTRICAL ROOM / A5</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="n">
         <v>0</v>
       </c>
@@ -2985,7 +2914,6 @@
         </is>
       </c>
       <c r="V48" s="5" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3006,7 +2934,6 @@
           <t>ELECTRICAL ROOM / B5</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="n">
         <v>1</v>
       </c>
@@ -3037,7 +2964,6 @@
         </is>
       </c>
       <c r="V49" s="5" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3091,7 +3017,6 @@
         </is>
       </c>
       <c r="V50" s="5" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3112,7 +3037,6 @@
           <t>ELECTRICAL ROOM / B5</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="n">
         <v>1</v>
       </c>
@@ -3143,7 +3067,6 @@
         </is>
       </c>
       <c r="V51" s="5" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3197,7 +3120,6 @@
         </is>
       </c>
       <c r="V52" s="5" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3218,7 +3140,6 @@
           <t>ELECTRICAL ROOM / A5</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
         <v>0</v>
       </c>
@@ -3249,7 +3170,6 @@
         </is>
       </c>
       <c r="V53" s="5" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3270,7 +3190,6 @@
           <t>ELECTRICAL ROOM / C5</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="n">
         <v>2</v>
       </c>
@@ -3301,7 +3220,6 @@
         </is>
       </c>
       <c r="V54" s="5" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3322,7 +3240,6 @@
           <t>ELECTRICAL ROOM / B5</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="n">
         <v>1</v>
       </c>
@@ -3353,7 +3270,6 @@
         </is>
       </c>
       <c r="V55" s="5" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3374,7 +3290,6 @@
           <t>ELECTRICAL ROOM / A5</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="n">
         <v>0</v>
       </c>
@@ -3405,7 +3320,6 @@
         </is>
       </c>
       <c r="V56" s="5" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3459,7 +3373,6 @@
         </is>
       </c>
       <c r="V57" s="5" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3480,7 +3393,6 @@
           <t>ELECTRICAL ROOM / B5</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
         <v>1</v>
       </c>
@@ -3511,7 +3423,6 @@
         </is>
       </c>
       <c r="V58" s="5" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3532,7 +3443,6 @@
           <t>ELECTRICAL ROOM / B5</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="n">
         <v>1</v>
       </c>
@@ -3563,7 +3473,6 @@
         </is>
       </c>
       <c r="V59" s="5" t="inlineStr"/>
-      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3584,7 +3493,6 @@
           <t>ELECTRICAL ROOM / A5</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="n">
         <v>0</v>
       </c>
@@ -3615,7 +3523,6 @@
         </is>
       </c>
       <c r="V60" s="5" t="inlineStr"/>
-      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3669,7 +3576,6 @@
         </is>
       </c>
       <c r="V61" s="5" t="inlineStr"/>
-      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3690,7 +3596,6 @@
           <t>ELECTRICAL ROOM / C5</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="n">
         <v>2</v>
       </c>
@@ -3698,7 +3603,7 @@
         <v>6</v>
       </c>
       <c r="H62" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3721,7 +3626,6 @@
         </is>
       </c>
       <c r="V62" s="5" t="inlineStr"/>
-      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3742,7 +3646,6 @@
           <t>ELECTRICAL ROOM / A5</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="n">
         <v>0</v>
       </c>
@@ -3773,7 +3676,6 @@
         </is>
       </c>
       <c r="V63" s="5" t="inlineStr"/>
-      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3794,7 +3696,6 @@
           <t>ELECTRICAL ROOM / B5</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
         <v>1</v>
       </c>
@@ -3825,7 +3726,6 @@
         </is>
       </c>
       <c r="V64" s="5" t="inlineStr"/>
-      <c r="X64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3846,7 +3746,6 @@
           <t>ELECTRICAL ROOM / A5</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
         <v>0</v>
       </c>
@@ -3877,7 +3776,6 @@
         </is>
       </c>
       <c r="V65" s="5" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3898,7 +3796,6 @@
           <t>ELECTRICAL ROOM / B5</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="n">
         <v>1</v>
       </c>
@@ -3929,7 +3826,6 @@
         </is>
       </c>
       <c r="V66" s="5" t="inlineStr"/>
-      <c r="X66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3983,7 +3879,6 @@
         </is>
       </c>
       <c r="V67" s="5" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4004,7 +3899,6 @@
           <t>ELECTRICAL ROOM / C5</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="n">
         <v>2</v>
       </c>
@@ -4035,7 +3929,6 @@
         </is>
       </c>
       <c r="V68" s="5" t="inlineStr"/>
-      <c r="X68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4056,7 +3949,6 @@
           <t>ELECTRICAL ROOM / A5</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="n">
         <v>0</v>
       </c>
@@ -4087,7 +3979,6 @@
         </is>
       </c>
       <c r="V69" s="5" t="inlineStr"/>
-      <c r="X69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4108,7 +3999,6 @@
           <t>ELECTRICAL ROOM / A5</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="n">
         <v>0</v>
       </c>
@@ -4139,7 +4029,6 @@
         </is>
       </c>
       <c r="V70" s="5" t="inlineStr"/>
-      <c r="X70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4160,7 +4049,6 @@
           <t>ELECTRICAL ROOM / C5</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="n">
         <v>2</v>
       </c>
@@ -4191,7 +4079,6 @@
         </is>
       </c>
       <c r="V71" s="5" t="inlineStr"/>
-      <c r="X71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4245,7 +4132,6 @@
         </is>
       </c>
       <c r="V72" s="5" t="inlineStr"/>
-      <c r="X72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4299,7 +4185,6 @@
         </is>
       </c>
       <c r="V73" s="5" t="inlineStr"/>
-      <c r="X73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4320,7 +4205,6 @@
           <t>ELECTRICAL ROOM / C5</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="n">
         <v>2</v>
       </c>
@@ -4351,7 +4235,6 @@
         </is>
       </c>
       <c r="V74" s="5" t="inlineStr"/>
-      <c r="X74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4382,7 +4265,7 @@
         <v>4</v>
       </c>
       <c r="H75" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4405,7 +4288,6 @@
         </is>
       </c>
       <c r="V75" s="5" t="inlineStr"/>
-      <c r="X75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4426,7 +4308,6 @@
           <t>ELECTRICAL ROOM / A5</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="n">
         <v>0</v>
       </c>
@@ -4482,7 +4363,6 @@
           <t>ELECTRICAL ROOM / A5</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
         <v>0</v>
       </c>
@@ -4538,7 +4418,6 @@
           <t>ELECTRICAL ROOM / A5</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
         <v>0</v>
       </c>
@@ -4546,7 +4425,7 @@
         <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4594,7 +4473,6 @@
           <t>ELECTRICAL ROOM / A5</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
         <v>0</v>
       </c>
@@ -4602,7 +4480,7 @@
         <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4650,7 +4528,6 @@
           <t>ELECTRICAL ROOM / A4</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
         <v>3</v>
       </c>
@@ -4676,7 +4553,6 @@
         </is>
       </c>
       <c r="V80" s="5" t="n"/>
-      <c r="X80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4697,7 +4573,6 @@
           <t>ELECTRICAL ROOM / A4</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>3</v>
       </c>
@@ -4723,7 +4598,6 @@
         </is>
       </c>
       <c r="V81" s="5" t="n"/>
-      <c r="X81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4744,7 +4618,6 @@
           <t>ELECTRICAL ROOM / A4</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
         <v>3</v>
       </c>
@@ -4770,7 +4643,6 @@
         </is>
       </c>
       <c r="V82" s="5" t="n"/>
-      <c r="X82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4791,7 +4663,6 @@
           <t>ELECTRICAL ROOM / A4</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
         <v>3</v>
       </c>
@@ -4817,7 +4688,6 @@
         </is>
       </c>
       <c r="V83" s="5" t="n"/>
-      <c r="X83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -4838,7 +4708,6 @@
           <t>ELECTRICAL ROOM / A4</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
         <v>3</v>
       </c>
@@ -4864,7 +4733,6 @@
         </is>
       </c>
       <c r="V84" s="5" t="n"/>
-      <c r="X84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4885,7 +4753,6 @@
           <t>ELECTRICAL ROOM / A4</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
         <v>3</v>
       </c>
@@ -4911,7 +4778,6 @@
         </is>
       </c>
       <c r="V85" s="5" t="n"/>
-      <c r="X85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -4932,7 +4798,6 @@
           <t>ELECTRICAL ROOM / A4</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
         <v>3</v>
       </c>
@@ -4958,7 +4823,6 @@
         </is>
       </c>
       <c r="V86" s="5" t="n"/>
-      <c r="X86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -4979,7 +4843,6 @@
           <t>ELECTRICAL ROOM / A4</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="n">
         <v>3</v>
       </c>
@@ -5005,7 +4868,6 @@
         </is>
       </c>
       <c r="V87" s="5" t="n"/>
-      <c r="X87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5026,7 +4888,6 @@
           <t>ELECTRICAL ROOM / A4</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="n">
         <v>3</v>
       </c>
@@ -5052,7 +4913,6 @@
         </is>
       </c>
       <c r="V88" s="5" t="n"/>
-      <c r="X88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5073,7 +4933,6 @@
           <t>ELECTRICAL ROOM / A4</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
         <v>3</v>
       </c>
@@ -5099,7 +4958,6 @@
         </is>
       </c>
       <c r="V89" s="5" t="n"/>
-      <c r="X89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5120,7 +4978,6 @@
           <t>ELECTRICAL ROOM / A4</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="n">
         <v>3</v>
       </c>
@@ -5146,7 +5003,6 @@
         </is>
       </c>
       <c r="V90" s="5" t="n"/>
-      <c r="X90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5167,7 +5023,6 @@
           <t>ELECTRICAL ROOM / A4</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
       <c r="F91" t="n">
         <v>3</v>
       </c>
@@ -5193,7 +5048,6 @@
         </is>
       </c>
       <c r="V91" s="5" t="n"/>
-      <c r="X91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5214,7 +5068,6 @@
           <t>ELECTRICAL ROOM / A4</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
       <c r="F92" t="n">
         <v>3</v>
       </c>
@@ -5240,7 +5093,6 @@
         </is>
       </c>
       <c r="V92" s="5" t="n"/>
-      <c r="X92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5261,7 +5113,6 @@
           <t>ELECTRICAL ROOM / A4</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" t="n">
         <v>3</v>
       </c>
@@ -5287,7 +5138,6 @@
         </is>
       </c>
       <c r="V93" s="5" t="n"/>
-      <c r="X93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5308,7 +5158,6 @@
           <t>ELECTRICAL ROOM / A4</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
       <c r="F94" t="n">
         <v>3</v>
       </c>
@@ -5334,7 +5183,6 @@
         </is>
       </c>
       <c r="V94" s="5" t="n"/>
-      <c r="X94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5355,7 +5203,6 @@
           <t>ELECTRICAL ROOM / A4</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
       <c r="F95" t="n">
         <v>3</v>
       </c>
@@ -5381,7 +5228,6 @@
         </is>
       </c>
       <c r="V95" s="5" t="n"/>
-      <c r="X95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -5402,7 +5248,6 @@
           <t>ELECTRICAL ROOM / A4</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
       <c r="F96" t="n">
         <v>3</v>
       </c>
@@ -5428,7 +5273,6 @@
         </is>
       </c>
       <c r="V96" s="5" t="n"/>
-      <c r="X96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -5449,7 +5293,6 @@
           <t>ELECTRICAL ROOM / A4</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
       <c r="F97" t="n">
         <v>3</v>
       </c>
@@ -5475,7 +5318,6 @@
         </is>
       </c>
       <c r="V97" s="5" t="n"/>
-      <c r="X97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -5496,7 +5338,6 @@
           <t>ELECTRICAL ROOM / A4</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
       <c r="F98" t="n">
         <v>3</v>
       </c>
@@ -5522,7 +5363,6 @@
         </is>
       </c>
       <c r="V98" s="5" t="n"/>
-      <c r="X98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -5543,7 +5383,6 @@
           <t>ELECTRICAL ROOM / A4</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
       <c r="F99" t="n">
         <v>3</v>
       </c>
@@ -5569,7 +5408,6 @@
         </is>
       </c>
       <c r="V99" s="5" t="n"/>
-      <c r="X99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -5590,7 +5428,6 @@
           <t>ELECTRICAL ROOM / A4</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
       <c r="F100" t="n">
         <v>3</v>
       </c>
@@ -5616,7 +5453,6 @@
         </is>
       </c>
       <c r="V100" s="5" t="n"/>
-      <c r="X100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -5637,7 +5473,6 @@
           <t>ELECTRICAL ROOM / A4</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
       <c r="F101" t="n">
         <v>3</v>
       </c>
@@ -5663,7 +5498,6 @@
         </is>
       </c>
       <c r="V101" s="5" t="n"/>
-      <c r="X101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -5684,7 +5518,6 @@
           <t>ELECTRICAL ROOM / A4</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
       <c r="F102" t="n">
         <v>3</v>
       </c>
@@ -5735,7 +5568,6 @@
           <t>ELECTRICAL ROOM / A4</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
       <c r="F103" t="n">
         <v>3</v>
       </c>
